--- a/data/trans_dic/P6903-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6903-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas</t>
+          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,4; 43,51</t>
+          <t>25,55; 43,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,75; 37,94</t>
+          <t>13,51; 35,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,39; 66,16</t>
+          <t>37,99; 67,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,65; 62,41</t>
+          <t>23,69; 60,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>22,09; 53,65</t>
+          <t>23,88; 53,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,25; 45,78</t>
+          <t>16,45; 47,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,1; 67,67</t>
+          <t>21,99; 66,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,43; 79,21</t>
+          <t>34,49; 82,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,57; 44,18</t>
+          <t>27,09; 43,56</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17,89; 36,29</t>
+          <t>18,21; 35,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39,12; 63,44</t>
+          <t>39,62; 63,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>33,47; 64,06</t>
+          <t>34,55; 64,53</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,34; 36,86</t>
+          <t>25,21; 36,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,59; 30,93</t>
+          <t>18,58; 30,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31,07; 43,93</t>
+          <t>30,3; 43,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,21; 39,7</t>
+          <t>26,35; 39,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,83; 41,41</t>
+          <t>24,54; 42,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,75; 47,33</t>
+          <t>28,92; 46,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,85; 51,56</t>
+          <t>34,18; 51,98</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>21,4; 43,65</t>
+          <t>22,03; 42,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,3; 36,16</t>
+          <t>26,38; 36,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,66; 34,71</t>
+          <t>24,71; 34,61</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>33,69; 44,45</t>
+          <t>34,17; 44,47</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>26,15; 38,84</t>
+          <t>25,98; 39,12</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,0; 40,72</t>
+          <t>18,37; 40,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,79; 36,41</t>
+          <t>9,9; 34,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,09; 42,75</t>
+          <t>18,58; 42,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,73; 50,99</t>
+          <t>24,64; 52,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,68; 36,8</t>
+          <t>14,94; 37,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,59; 44,96</t>
+          <t>17,41; 46,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,15; 52,42</t>
+          <t>27,02; 51,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>36,17; 54,12</t>
+          <t>35,93; 54,62</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,46; 35,47</t>
+          <t>19,23; 35,2</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,06; 36,04</t>
+          <t>16,16; 35,13</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,35; 44,92</t>
+          <t>27,58; 43,59</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,31; 50,4</t>
+          <t>34,1; 49,83</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,29; 36,11</t>
+          <t>27,44; 36,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,24; 28,21</t>
+          <t>19,41; 28,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,1; 43,73</t>
+          <t>33,27; 44,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,18; 40,45</t>
+          <t>28,92; 40,28</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,09; 37,85</t>
+          <t>24,95; 36,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,46; 41,47</t>
+          <t>28,64; 41,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,45; 48,95</t>
+          <t>34,33; 47,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,63; 45,06</t>
+          <t>27,84; 45,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,76; 35,01</t>
+          <t>27,74; 35,08</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,58; 32,38</t>
+          <t>24,35; 32,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,57; 44,48</t>
+          <t>35,5; 44,26</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,99; 40,91</t>
+          <t>30,96; 41,46</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas</t>
+          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28261; 48423</t>
+          <t>28434; 48813</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7936; 21893</t>
+          <t>7795; 20725</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21895; 36773</t>
+          <t>21115; 37364</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7787; 18233</t>
+          <t>6922; 17592</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8298; 20154</t>
+          <t>8972; 20123</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6163; 17365</t>
+          <t>6239; 17891</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3983; 12197</t>
+          <t>3963; 12066</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8103; 19791</t>
+          <t>8617; 20602</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41045; 65767</t>
+          <t>40330; 64845</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17108; 34708</t>
+          <t>17417; 34113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28793; 46695</t>
+          <t>29161; 46581</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18140; 34718</t>
+          <t>18724; 34976</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72700; 105755</t>
+          <t>72330; 104963</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40805; 67915</t>
+          <t>40785; 67819</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71280; 100770</t>
+          <t>69499; 100561</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62110; 94072</t>
+          <t>62442; 93624</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29442; 49099</t>
+          <t>29103; 49960</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37493; 61734</t>
+          <t>37723; 60556</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42161; 64223</t>
+          <t>42572; 64750</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51000; 104042</t>
+          <t>52504; 102442</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>106645; 146628</t>
+          <t>106961; 148635</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86320; 121476</t>
+          <t>86490; 121130</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>119230; 157337</t>
+          <t>120960; 157405</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>124293; 184613</t>
+          <t>123473; 185928</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14814; 30161</t>
+          <t>13606; 29905</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4973; 16782</t>
+          <t>4563; 16064</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11491; 27158</t>
+          <t>11806; 26859</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16499; 35453</t>
+          <t>17134; 36441</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9392; 23547</t>
+          <t>9560; 23808</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7684; 20827</t>
+          <t>8066; 21423</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20745; 38637</t>
+          <t>19915; 38212</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32557; 48719</t>
+          <t>32338; 49164</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26867; 48968</t>
+          <t>26542; 48594</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14840; 33307</t>
+          <t>14933; 32461</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37534; 61648</t>
+          <t>37847; 59823</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54731; 80410</t>
+          <t>54405; 79495</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>128890; 170546</t>
+          <t>129613; 170683</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62209; 91214</t>
+          <t>62762; 93349</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>115346; 152405</t>
+          <t>115958; 154128</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97953; 135781</t>
+          <t>97071; 135224</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>55237; 83314</t>
+          <t>54919; 81376</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61107; 89027</t>
+          <t>61476; 88549</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>76669; 105873</t>
+          <t>74264; 103788</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>97629; 159213</t>
+          <t>98387; 159419</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>192224; 242444</t>
+          <t>192104; 242897</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>132229; 174235</t>
+          <t>130995; 173126</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>200880; 251239</t>
+          <t>200526; 249980</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>213549; 281916</t>
+          <t>213335; 285709</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6903-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6903-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>43,42%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,55; 43,86</t>
+          <t>25,83; 44,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,51; 35,92</t>
+          <t>14,32; 37,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37,99; 67,22</t>
+          <t>38,03; 67,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,69; 60,22</t>
+          <t>29,07; 61,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>23,88; 53,56</t>
+          <t>22,36; 54,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,45; 47,16</t>
+          <t>16,06; 45,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,99; 66,94</t>
+          <t>22,13; 67,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,49; 82,46</t>
+          <t>25,96; 57,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27,09; 43,56</t>
+          <t>27,48; 43,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,21; 35,67</t>
+          <t>17,7; 36,7</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39,62; 63,28</t>
+          <t>39,56; 63,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,55; 64,53</t>
+          <t>31,51; 55,82</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>25,21; 36,58</t>
+          <t>25,57; 37,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,58; 30,89</t>
+          <t>19,2; 30,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30,3; 43,84</t>
+          <t>31,01; 43,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,35; 39,52</t>
+          <t>27,35; 40,77</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,54; 42,13</t>
+          <t>23,87; 40,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,92; 46,43</t>
+          <t>29,56; 46,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,18; 51,98</t>
+          <t>34,09; 52,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,03; 42,98</t>
+          <t>36,17; 47,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,38; 36,65</t>
+          <t>27,05; 36,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24,71; 34,61</t>
+          <t>24,26; 34,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34,17; 44,47</t>
+          <t>34,17; 44,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>25,98; 39,12</t>
+          <t>33,22; 41,86</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>39,55%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,71%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>42,99%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,37; 40,37</t>
+          <t>18,98; 40,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,9; 34,86</t>
+          <t>10,26; 35,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,58; 42,28</t>
+          <t>18,96; 43,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24,64; 52,41</t>
+          <t>26,68; 53,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,94; 37,21</t>
+          <t>14,04; 35,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,41; 46,25</t>
+          <t>16,66; 45,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,02; 51,84</t>
+          <t>28,98; 51,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,93; 54,62</t>
+          <t>36,81; 54,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>19,23; 35,2</t>
+          <t>19,01; 34,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,16; 35,13</t>
+          <t>16,44; 36,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,58; 43,59</t>
+          <t>26,45; 43,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>34,1; 49,83</t>
+          <t>35,62; 51,1</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>39,28%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>27,44; 36,14</t>
+          <t>27,22; 35,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,41; 28,87</t>
+          <t>19,43; 29,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>33,27; 44,23</t>
+          <t>33,69; 44,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,92; 40,28</t>
+          <t>30,44; 41,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>24,95; 36,97</t>
+          <t>25,12; 37,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,64; 41,25</t>
+          <t>27,66; 41,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,33; 47,98</t>
+          <t>34,78; 48,52</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,84; 45,11</t>
+          <t>38,06; 47,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,74; 35,08</t>
+          <t>27,72; 34,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24,35; 32,18</t>
+          <t>24,46; 32,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,5; 44,26</t>
+          <t>35,43; 44,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,96; 41,46</t>
+          <t>35,65; 43,17</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12446</t>
+          <t>16154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13437</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25883</t>
+          <t>26363</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28434; 48813</t>
+          <t>28745; 48968</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7795; 20725</t>
+          <t>8264; 21897</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21115; 37364</t>
+          <t>21139; 37306</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6922; 17592</t>
+          <t>10527; 22309</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8972; 20123</t>
+          <t>8400; 20655</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6239; 17891</t>
+          <t>6094; 17276</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3963; 12066</t>
+          <t>3989; 12109</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8617; 20602</t>
+          <t>6363; 14155</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>40330; 64845</t>
+          <t>40899; 64763</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17417; 34113</t>
+          <t>16931; 35095</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29161; 46581</t>
+          <t>29115; 46769</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18724; 34976</t>
+          <t>19132; 33892</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77377</t>
+          <t>90799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>84114</t>
+          <t>91705</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>161491</t>
+          <t>182505</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>72330; 104963</t>
+          <t>73384; 106178</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>40785; 67819</t>
+          <t>42151; 66337</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69499; 100561</t>
+          <t>71128; 100319</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62442; 93624</t>
+          <t>72998; 108803</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29103; 49960</t>
+          <t>28305; 48107</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37723; 60556</t>
+          <t>38554; 61134</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42572; 64750</t>
+          <t>42467; 65428</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52504; 102442</t>
+          <t>79892; 105490</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>106961; 148635</t>
+          <t>109676; 147243</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>86490; 121130</t>
+          <t>84908; 120766</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>120960; 157405</t>
+          <t>120956; 157435</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>123473; 185928</t>
+          <t>162018; 204154</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>25362</t>
+          <t>30755</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>40663</t>
+          <t>45116</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>66025</t>
+          <t>75871</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13606; 29905</t>
+          <t>14061; 29838</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4563; 16064</t>
+          <t>4727; 16281</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11806; 26859</t>
+          <t>12048; 27700</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17134; 36441</t>
+          <t>20751; 41978</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9560; 23808</t>
+          <t>8985; 22704</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8066; 21423</t>
+          <t>7718; 21082</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19915; 38212</t>
+          <t>21358; 38199</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>32338; 49164</t>
+          <t>36333; 53705</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26542; 48594</t>
+          <t>26242; 47445</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14933; 32461</t>
+          <t>15190; 33690</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37847; 59823</t>
+          <t>36303; 59446</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54405; 79495</t>
+          <t>62854; 90173</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>115185</t>
+          <t>137708</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>138213</t>
+          <t>147031</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>253399</t>
+          <t>284739</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>129613; 170683</t>
+          <t>128558; 169966</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62762; 93349</t>
+          <t>62831; 93822</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>115958; 154128</t>
+          <t>117394; 154027</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97071; 135224</t>
+          <t>115919; 159265</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54919; 81376</t>
+          <t>55287; 82728</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>61476; 88549</t>
+          <t>59371; 88706</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>74264; 103788</t>
+          <t>75223; 104953</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>98387; 159419</t>
+          <t>130938; 162243</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>192104; 242897</t>
+          <t>191958; 242244</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>130995; 173126</t>
+          <t>131593; 176633</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>200526; 249980</t>
+          <t>200130; 249001</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>213335; 285709</t>
+          <t>258465; 312920</t>
         </is>
       </c>
     </row>
